--- a/features/feature_importance_all.xlsx
+++ b/features/feature_importance_all.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,7 +444,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>446.3855285644531</v>
+        <v>2472.65185546875</v>
       </c>
     </row>
     <row r="3">
@@ -454,87 +454,77 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>50.93661117553711</v>
+        <v>563.8460693359375</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>metaphone_match</t>
+          <t>token_set_ratio</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.52863311767578</v>
+        <v>144.1263427734375</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Levenshtein</t>
+          <t>jaccard</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.20233535766602</v>
+        <v>112.0286865234375</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>similar_gender</t>
+          <t>Levenshtein</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.50641059875488</v>
+        <v>80.4964599609375</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>jaccard</t>
+          <t>jaro_sim</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17.8316478729248</v>
+        <v>70.02059173583984</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>token_set_ratio</t>
+          <t>sbert_sim</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16.42995262145996</v>
+        <v>47.7373161315918</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>jaro_sim</t>
+          <t>metaphone_match</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12.39710235595703</v>
+        <v>35.02665328979492</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>sbert_sim</t>
+          <t>similar_gender</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9.330876350402832</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>complete_overlap</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
+        <v>12.84872341156006</v>
       </c>
     </row>
   </sheetData>
@@ -548,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -561,11 +551,11 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>jaro_sim</t>
+          <t>token_set_ratio</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>532</v>
+        <v>641</v>
       </c>
     </row>
     <row r="3">
@@ -575,27 +565,27 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>501</v>
+        <v>487</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>token_set_ratio</t>
+          <t>jaro_sim</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>459</v>
+        <v>435</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>sbert_sim</t>
+          <t>jaccard</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>304</v>
+        <v>369</v>
       </c>
     </row>
     <row r="6">
@@ -605,17 +595,17 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>jaccard</t>
+          <t>sbert_sim</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>277</v>
+        <v>294</v>
       </c>
     </row>
     <row r="8">
@@ -625,7 +615,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9">
@@ -635,7 +625,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10">
@@ -645,17 +635,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>complete_overlap</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -686,97 +666,87 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1868.58349609375</v>
+        <v>2257.194580078125</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>metaphone_match</t>
+          <t>cosine_sim</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>706.8523559570312</v>
+        <v>554.5723266601562</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>cosine_sim</t>
+          <t>token_set_ratio</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>511.8167419433594</v>
+        <v>467.9760131835938</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Levenshtein</t>
+          <t>jaro_sim</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>432.7401733398438</v>
+        <v>462.7060852050781</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>token_set_ratio</t>
+          <t>jaccard</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>394.1046142578125</v>
+        <v>363.4585876464844</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>similar_gender</t>
+          <t>Levenshtein</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>350.3339233398438</v>
+        <v>344.2289123535156</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jaccard</t>
+          <t>metaphone_match</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>342.8349914550781</v>
+        <v>251.843017578125</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>jaro_sim</t>
+          <t>sbert_sim</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>302.6389465332031</v>
+        <v>170.1033325195312</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>sbert_sim</t>
+          <t>similar_gender</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>277.3922119140625</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>complete_overlap</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
+        <v>21.2491283416748</v>
       </c>
     </row>
   </sheetData>
